--- a/dataset/history.xlsx
+++ b/dataset/history.xlsx
@@ -418,7 +418,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AH32"/>
+  <dimension ref="A1:AH51"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="14.5"/>
   <cols>
     <col width="3.1796875" bestFit="1" customWidth="1" min="1" max="1"/>
@@ -3651,7 +3651,7 @@
         <v>31</v>
       </c>
       <c r="B32" s="3" t="n">
-        <v>46188.38525487154</v>
+        <v>46188.38525487269</v>
       </c>
       <c r="C32" t="inlineStr">
         <is>
@@ -3741,18 +3741,2022 @@
           <t>Mirip</t>
         </is>
       </c>
-      <c r="W32" t="inlineStr"/>
-      <c r="X32" t="inlineStr"/>
-      <c r="Y32" t="inlineStr"/>
-      <c r="Z32" t="inlineStr"/>
-      <c r="AA32" t="inlineStr"/>
-      <c r="AB32" t="inlineStr"/>
-      <c r="AC32" t="inlineStr"/>
-      <c r="AD32" t="inlineStr"/>
-      <c r="AE32" t="inlineStr"/>
-      <c r="AF32" t="inlineStr"/>
-      <c r="AG32" t="inlineStr"/>
-      <c r="AH32" t="inlineStr"/>
+    </row>
+    <row r="33">
+      <c r="A33" t="n">
+        <v>32</v>
+      </c>
+      <c r="B33" s="3" t="n">
+        <v>46191.47893186343</v>
+      </c>
+      <c r="C33" t="inlineStr">
+        <is>
+          <t>judul</t>
+        </is>
+      </c>
+      <c r="D33" t="inlineStr">
+        <is>
+          <t>rancang bangun pemantau berkurangnya cairan infus berbasis arduino dan iot klinik azzaniyah nurul jadid</t>
+        </is>
+      </c>
+      <c r="E33" t="inlineStr">
+        <is>
+          <t>rancang bangun pemantau berkurangnya cairan infus berbasis arduino dan iot klinik azzaniyah nurul jadid</t>
+        </is>
+      </c>
+      <c r="F33" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="G33" t="inlineStr">
+        <is>
+          <t>Sangat Unik</t>
+        </is>
+      </c>
+      <c r="H33" t="inlineStr">
+        <is>
+          <t>monitoring infus dan pulse heart rate berbasis iot</t>
+        </is>
+      </c>
+      <c r="I33" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="J33" t="inlineStr">
+        <is>
+          <t>Mirip</t>
+        </is>
+      </c>
+      <c r="K33" t="inlineStr">
+        <is>
+          <t>rekam data self manajemen cairan pada pasien gagal ginjal kronis yang menjalani terapi hemodialisa di rsud abdoer rahem berbasis android</t>
+        </is>
+      </c>
+      <c r="L33" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="M33" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N33" t="inlineStr">
+        <is>
+          <t>prediksi jenis penyakit pasien berdasarkan temperatur rata-rata dan curah hujan di klinik az-zainiyah menggunakan metode backpropagation</t>
+        </is>
+      </c>
+      <c r="O33" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="P33" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q33" t="inlineStr">
+        <is>
+          <t>perancangan smart klinik berbasis mikrokontroler nodemcu esp32</t>
+        </is>
+      </c>
+      <c r="R33" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="S33" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T33" t="inlineStr">
+        <is>
+          <t>sistem monitoring kesehatan air dengan constructed wetlands berbasis mikrokontroler</t>
+        </is>
+      </c>
+      <c r="U33" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="V33" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="34">
+      <c r="A34" t="n">
+        <v>33</v>
+      </c>
+      <c r="B34" s="3" t="n">
+        <v>46191.47974989584</v>
+      </c>
+      <c r="C34" t="inlineStr">
+        <is>
+          <t>judul</t>
+        </is>
+      </c>
+      <c r="D34" t="inlineStr">
+        <is>
+          <t>sss</t>
+        </is>
+      </c>
+      <c r="E34" t="inlineStr">
+        <is>
+          <t>sss</t>
+        </is>
+      </c>
+      <c r="F34" t="n">
+        <v>1</v>
+      </c>
+      <c r="G34" t="inlineStr">
+        <is>
+          <t>Sangat Unik</t>
+        </is>
+      </c>
+      <c r="H34" t="inlineStr">
+        <is>
+          <t>jaringan dan komunikasi data</t>
+        </is>
+      </c>
+      <c r="I34" t="n">
+        <v>0.37</v>
+      </c>
+      <c r="J34" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="K34" t="inlineStr">
+        <is>
+          <t>evolusi jaringan mobile</t>
+        </is>
+      </c>
+      <c r="L34" t="n">
+        <v>0.26</v>
+      </c>
+      <c r="M34" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N34" t="inlineStr">
+        <is>
+          <t>buku ajar keamanan data dan informasi</t>
+        </is>
+      </c>
+      <c r="O34" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P34" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q34" t="inlineStr">
+        <is>
+          <t>game edukasi kebersihan pantai duta berbasis android</t>
+        </is>
+      </c>
+      <c r="R34" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="S34" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T34" t="inlineStr">
+        <is>
+          <t>sistem informasi pendataan pengunjung perpustakaan unuja menggunakan qrcode</t>
+        </is>
+      </c>
+      <c r="U34" t="n">
+        <v>0.23</v>
+      </c>
+      <c r="V34" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="35">
+      <c r="A35" t="n">
+        <v>34</v>
+      </c>
+      <c r="B35" s="3" t="n">
+        <v>46193.52905578704</v>
+      </c>
+      <c r="C35" t="inlineStr">
+        <is>
+          <t>judul</t>
+        </is>
+      </c>
+      <c r="D35" t="inlineStr">
+        <is>
+          <t>SIG Pemetaan Hewan Ternak Sapi Potong Berdasarkan Ketersediaan Lahan di Kabupaten Probolinggo</t>
+        </is>
+      </c>
+      <c r="E35" t="inlineStr">
+        <is>
+          <t>sig pemetaan hewan ternak sapi potong berdasarkan ketersediaan lahan di kabupaten probolinggo</t>
+        </is>
+      </c>
+      <c r="F35" t="n">
+        <v>0</v>
+      </c>
+      <c r="G35" t="inlineStr">
+        <is>
+          <t>Tidak Unik</t>
+        </is>
+      </c>
+      <c r="H35" t="inlineStr">
+        <is>
+          <t>sig pemetaan hewan ternak sapi potong berdasarkan ketersediaan lahan di kabupaten probolinggo</t>
+        </is>
+      </c>
+      <c r="I35" t="n">
+        <v>1</v>
+      </c>
+      <c r="J35" t="inlineStr">
+        <is>
+          <t>Sangat Mirip</t>
+        </is>
+      </c>
+      <c r="K35" t="inlineStr">
+        <is>
+          <t>aplikasi manajemen ternak sapi perah di kud krucil berbasis web framework django</t>
+        </is>
+      </c>
+      <c r="L35" t="n">
+        <v>0.82</v>
+      </c>
+      <c r="M35" t="inlineStr">
+        <is>
+          <t>Sangat Mirip</t>
+        </is>
+      </c>
+      <c r="N35" t="inlineStr">
+        <is>
+          <t>sistem monitoring perkembangan ternak sapi berbasis web menggunakan framework codeigniter studi kasus ternak tani lestari desa kotaanyar</t>
+        </is>
+      </c>
+      <c r="O35" t="n">
+        <v>0.6899999999999999</v>
+      </c>
+      <c r="P35" t="inlineStr">
+        <is>
+          <t>Mirip</t>
+        </is>
+      </c>
+      <c r="Q35" t="inlineStr">
+        <is>
+          <t>sistem informasi kartu ternak sapi berbasis web di dinas peternakan dan kesehatan hewan probolinggo</t>
+        </is>
+      </c>
+      <c r="R35" t="n">
+        <v>0.67</v>
+      </c>
+      <c r="S35" t="inlineStr">
+        <is>
+          <t>Mirip</t>
+        </is>
+      </c>
+      <c r="T35" t="inlineStr">
+        <is>
+          <t>pemetaan peternak kelinci berbasis android di kabupaten probolinggo</t>
+        </is>
+      </c>
+      <c r="U35" t="n">
+        <v>0.65</v>
+      </c>
+      <c r="V35" t="inlineStr">
+        <is>
+          <t>Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="36">
+      <c r="A36" t="n">
+        <v>35</v>
+      </c>
+      <c r="B36" s="3" t="n">
+        <v>46194.36828618056</v>
+      </c>
+      <c r="C36" t="inlineStr">
+        <is>
+          <t>deskripsi</t>
+        </is>
+      </c>
+      <c r="D36" t="inlineStr">
+        <is>
+          <t>waterfall</t>
+        </is>
+      </c>
+      <c r="E36" t="inlineStr">
+        <is>
+          <t>waterfall</t>
+        </is>
+      </c>
+      <c r="F36" t="n">
+        <v>1</v>
+      </c>
+      <c r="G36" t="inlineStr">
+        <is>
+          <t>Sangat Unik</t>
+        </is>
+      </c>
+      <c r="H36" t="inlineStr">
+        <is>
+          <t>untuk mengetahui seberapa kuat atau seberapa cepat bunyi ultrasonic ketika melewati medan berpasir yang berbeda dan bisa di pakai oleh para ahli geologi di lapangan</t>
+        </is>
+      </c>
+      <c r="I36" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J36" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="K36" t="inlineStr">
+        <is>
+          <t>kontrol level pada degasifier tank menggunakan feedback control karena nilai keluaran yang dihasilkan dari sistem akan dibandingkan dengan nilai set point nilai set point pada level degasifier tank yaitu sebesar 3000mm</t>
+        </is>
+      </c>
+      <c r="L36" t="n">
+        <v>0.22</v>
+      </c>
+      <c r="M36" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N36" t="inlineStr">
+        <is>
+          <t>perancangan windmill design bentuk ulir untuk menggerakkan water pump adalah suatu alat untuk memompa air menggunakan kincir angin alat ini dirancang agar meringankan masyarakat dalam mengambil air dan juga alat ini dibuat untuk mengurangi pemanasan global serta mengganti sumber daya alam menggunakan energi fosil yang saat ini mulai menipis</t>
+        </is>
+      </c>
+      <c r="O36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="P36" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q36" t="inlineStr">
+        <is>
+          <t>penelitian ini ingin menjelaskan secara sederhana bagaimana algoritma naive bayes bekerja dan bagaimana algoritma ini dapat digunakan dalam kehidupan sehari-hari naive bayes adalah metode yang membantu komputer untuk mengelompokkan data berdasarkan beberapa fitur penelitian ini akan menjelaskan prinsip dasar dari naive bayes dan bagaimana cara kerjanya termasuk kelebihan dan kekurangannya kemudian akan ditampilkan contoh-contoh nyata penggunaan naive bayes contoh studi kasus dan hasil eksperimen akan disertakan untuk menampilkan kinerja algoritma ini juga akan dibahas cara mengatasi tantangan seperti data yang tidak seimbang dan pemilihan fitur yang relevan penelitian ini diharapkan memberikan wawasan yang bermanfaat bagi mereka yang ingin menggunakan naive bayes</t>
+        </is>
+      </c>
+      <c r="R36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="S36" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T36" t="inlineStr">
+        <is>
+          <t>merancang dan membuat sebuah objek digital yang menggunakan arduino uno sebagai pusat pengelolaan data water flow sensor yf-s201digunakan sebagai sensor pengukur kecepatan aliran air objek ini akan mampu mengukur air limbah perdetiknya meningkatkan ketelitian pengukuran dan memberikan data yang lebih real-time</t>
+        </is>
+      </c>
+      <c r="U36" t="n">
+        <v>0.2</v>
+      </c>
+      <c r="V36" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="37">
+      <c r="A37" t="n">
+        <v>36</v>
+      </c>
+      <c r="B37" s="3" t="n">
+        <v>46194.36865222222</v>
+      </c>
+      <c r="C37" t="inlineStr">
+        <is>
+          <t>judul</t>
+        </is>
+      </c>
+      <c r="D37" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="E37" t="inlineStr">
+        <is>
+          <t>lstm</t>
+        </is>
+      </c>
+      <c r="F37" t="n">
+        <v>1</v>
+      </c>
+      <c r="G37" t="inlineStr">
+        <is>
+          <t>Sangat Unik</t>
+        </is>
+      </c>
+      <c r="H37" t="inlineStr">
+        <is>
+          <t>jaringan dan komunikasi data</t>
+        </is>
+      </c>
+      <c r="I37" t="n">
+        <v>0.3</v>
+      </c>
+      <c r="J37" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="K37" t="inlineStr">
+        <is>
+          <t>aplikasi monitoring perguruan tinggi menggunakan vue js di lldikti 7</t>
+        </is>
+      </c>
+      <c r="L37" t="n">
+        <v>0.28</v>
+      </c>
+      <c r="M37" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N37" t="inlineStr">
+        <is>
+          <t>aplikasi nuruljadid net berbasis mobile</t>
+        </is>
+      </c>
+      <c r="O37" t="n">
+        <v>0.25</v>
+      </c>
+      <c r="P37" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q37" t="inlineStr">
+        <is>
+          <t>analisis kinerja sistem informasi cdc universitas nurul jadid dengan menggunakan metode pieces</t>
+        </is>
+      </c>
+      <c r="R37" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="S37" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T37" t="inlineStr">
+        <is>
+          <t>perancangan dan implementasi portal berita berbasis website multiuser dengan menggunakan bahasa pemrograman python dan database mysql</t>
+        </is>
+      </c>
+      <c r="U37" t="n">
+        <v>0.24</v>
+      </c>
+      <c r="V37" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="38">
+      <c r="A38" t="n">
+        <v>37</v>
+      </c>
+      <c r="B38" s="3" t="n">
+        <v>46194.36886420139</v>
+      </c>
+      <c r="C38" t="inlineStr">
+        <is>
+          <t>judul</t>
+        </is>
+      </c>
+      <c r="D38" t="inlineStr">
+        <is>
+          <t>tes</t>
+        </is>
+      </c>
+      <c r="E38" t="inlineStr">
+        <is>
+          <t>tes</t>
+        </is>
+      </c>
+      <c r="F38" t="n">
+        <v>1</v>
+      </c>
+      <c r="G38" t="inlineStr">
+        <is>
+          <t>Sangat Unik</t>
+        </is>
+      </c>
+      <c r="H38" t="inlineStr">
+        <is>
+          <t>aplikasi reliabilitas soal tes pada soal tes obyektif berbasis website</t>
+        </is>
+      </c>
+      <c r="I38" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J38" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="K38" t="inlineStr">
+        <is>
+          <t>aplikasi perhitungan reliabilitas soal tes berbasis java</t>
+        </is>
+      </c>
+      <c r="L38" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="M38" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N38" t="inlineStr">
+        <is>
+          <t>metode clustering pada tes masuk peserta didik menggunakan django</t>
+        </is>
+      </c>
+      <c r="O38" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="P38" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q38" t="inlineStr">
+        <is>
+          <t>sistem rekomendasi mata kuliah pilihan menggunakan metode item-based collaborative filtering</t>
+        </is>
+      </c>
+      <c r="R38" t="n">
+        <v>0.4</v>
+      </c>
+      <c r="S38" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T38" t="inlineStr">
+        <is>
+          <t>sistem informasi pendaftaran uji kompetensi lembaga universitas nurul jadid berbasis web</t>
+        </is>
+      </c>
+      <c r="U38" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V38" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="39">
+      <c r="A39" t="n">
+        <v>38</v>
+      </c>
+      <c r="B39" s="3" t="n">
+        <v>46194.36901413195</v>
+      </c>
+      <c r="C39" t="inlineStr">
+        <is>
+          <t>judul</t>
+        </is>
+      </c>
+      <c r="D39" t="inlineStr">
+        <is>
+          <t>sentimen</t>
+        </is>
+      </c>
+      <c r="E39" t="inlineStr">
+        <is>
+          <t>sentimen</t>
+        </is>
+      </c>
+      <c r="F39" t="n">
+        <v>1</v>
+      </c>
+      <c r="G39" t="inlineStr">
+        <is>
+          <t>Sangat Unik</t>
+        </is>
+      </c>
+      <c r="H39" t="inlineStr">
+        <is>
+          <t>analisis sentimen mahasiswa terhadap proses pembelajaran di universitas nurul jadid menggunakan metode support vector machine</t>
+        </is>
+      </c>
+      <c r="I39" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="J39" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="K39" t="inlineStr">
+        <is>
+          <t>analisis sentimen ulasan aplikasi pembelajaran duolinggo di playstore menggunakan distilbert</t>
+        </is>
+      </c>
+      <c r="L39" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="M39" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N39" t="inlineStr">
+        <is>
+          <t>analisis sentimen review aplikasi zenius dan ruangguru menggunakan metode support vector machine</t>
+        </is>
+      </c>
+      <c r="O39" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="P39" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q39" t="inlineStr">
+        <is>
+          <t>analisis sentimen pada imdb movie rating menggunakan algoritma feature text extraction</t>
+        </is>
+      </c>
+      <c r="R39" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="S39" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T39" t="inlineStr">
+        <is>
+          <t>analisis sentimen kuesioner mahasiswa terhadap kampus universitas nurul jadid menggunakan metode deep neural network dnn</t>
+        </is>
+      </c>
+      <c r="U39" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="V39" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="40">
+      <c r="A40" t="n">
+        <v>39</v>
+      </c>
+      <c r="B40" s="3" t="n">
+        <v>46198.34003766203</v>
+      </c>
+      <c r="C40" t="inlineStr">
+        <is>
+          <t>judul</t>
+        </is>
+      </c>
+      <c r="D40" t="inlineStr">
+        <is>
+          <t>rancang bangun pemantau berkurangnya cairan infus berbasis arduino dan iot klinik azzaniyah nurul jadid</t>
+        </is>
+      </c>
+      <c r="E40" t="inlineStr">
+        <is>
+          <t>rancang bangun pemantau berkurangnya cairan infus berbasis arduino dan iot klinik azzaniyah nurul jadid</t>
+        </is>
+      </c>
+      <c r="F40" t="n">
+        <v>0.84</v>
+      </c>
+      <c r="G40" t="inlineStr">
+        <is>
+          <t>Sangat Unik</t>
+        </is>
+      </c>
+      <c r="H40" t="inlineStr">
+        <is>
+          <t>monitoring infus dan pulse heart rate berbasis iot</t>
+        </is>
+      </c>
+      <c r="I40" t="n">
+        <v>0.66</v>
+      </c>
+      <c r="J40" t="inlineStr">
+        <is>
+          <t>Mirip</t>
+        </is>
+      </c>
+      <c r="K40" t="inlineStr">
+        <is>
+          <t>aplikasi sensor tekanan pada tabung oksigen berbasis iot di rumah sakit waluyo jati menggunakan hp android</t>
+        </is>
+      </c>
+      <c r="L40" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M40" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N40" t="inlineStr">
+        <is>
+          <t>rekam data self manajemen cairan pada pasien gagal ginjal kronis yang menjalani terapi hemodialisa di rsud abdoer rahem berbasis android</t>
+        </is>
+      </c>
+      <c r="O40" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="P40" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q40" t="inlineStr">
+        <is>
+          <t>rancang bangun sistem monitoring arus tegangan listrik dan debit air pada pembangkit listrik tenaga mikrohidro berbasis internet of thing iot</t>
+        </is>
+      </c>
+      <c r="R40" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S40" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T40" t="inlineStr">
+        <is>
+          <t>sistem monitoring smart klinik berbasis internet of things iot</t>
+        </is>
+      </c>
+      <c r="U40" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="V40" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="41">
+      <c r="A41" t="n">
+        <v>40</v>
+      </c>
+      <c r="B41" s="3" t="n">
+        <v>46198.34096513889</v>
+      </c>
+      <c r="C41" t="inlineStr">
+        <is>
+          <t>judul</t>
+        </is>
+      </c>
+      <c r="D41" t="inlineStr">
+        <is>
+          <t>Sistem Informasi Surat Perintah Perjalanan Dinas di Dinas Komunikasi dan Informatika Kabupaten Situbondo Berbasis WEB</t>
+        </is>
+      </c>
+      <c r="E41" t="inlineStr">
+        <is>
+          <t>sistem informasi surat perintah perjalanan dinas di dinas komunikasi dan informatika kabupaten situbondo berbasis web</t>
+        </is>
+      </c>
+      <c r="F41" t="n">
+        <v>0.18</v>
+      </c>
+      <c r="G41" t="inlineStr">
+        <is>
+          <t>Tidak Unik</t>
+        </is>
+      </c>
+      <c r="H41" t="inlineStr">
+        <is>
+          <t>aplikasi surat perintah perjalanan dinas berbasis web studi kasus diskominfo kabupaten probolinggo</t>
+        </is>
+      </c>
+      <c r="I41" t="n">
+        <v>0.93</v>
+      </c>
+      <c r="J41" t="inlineStr">
+        <is>
+          <t>Sangat Mirip</t>
+        </is>
+      </c>
+      <c r="K41" t="inlineStr">
+        <is>
+          <t>aplikasi pengolahan surat perintah perjalanan dinas dengan global positioning system gps pada diskominfo kabupaten probolinggo berbasis web</t>
+        </is>
+      </c>
+      <c r="L41" t="n">
+        <v>0.86</v>
+      </c>
+      <c r="M41" t="inlineStr">
+        <is>
+          <t>Sangat Mirip</t>
+        </is>
+      </c>
+      <c r="N41" t="inlineStr">
+        <is>
+          <t>perancangan sistem monitoring surat perintah perjalanan dinas dengan mobile app android di universitas nurul jadid</t>
+        </is>
+      </c>
+      <c r="O41" t="n">
+        <v>0.8</v>
+      </c>
+      <c r="P41" t="inlineStr">
+        <is>
+          <t>Sangat Mirip</t>
+        </is>
+      </c>
+      <c r="Q41" t="inlineStr">
+        <is>
+          <t>sistem informasi monitoring perjalanan dinas di universitas nurul jadid berbasis web</t>
+        </is>
+      </c>
+      <c r="R41" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="S41" t="inlineStr">
+        <is>
+          <t>Mirip</t>
+        </is>
+      </c>
+      <c r="T41" t="inlineStr">
+        <is>
+          <t>rancang bangun aplikasi surat perintah perjalanan dinas sppd menggunakan framework codeigniter ci di universitas nurul jadid</t>
+        </is>
+      </c>
+      <c r="U41" t="n">
+        <v>0.74</v>
+      </c>
+      <c r="V41" t="inlineStr">
+        <is>
+          <t>Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="42">
+      <c r="A42" t="n">
+        <v>41</v>
+      </c>
+      <c r="B42" s="3" t="n">
+        <v>46198.34279633102</v>
+      </c>
+      <c r="C42" t="inlineStr">
+        <is>
+          <t>judul</t>
+        </is>
+      </c>
+      <c r="D42" t="inlineStr">
+        <is>
+          <t>Sistem Penilaian Judul Tugas Akhir Berbasis Indobert</t>
+        </is>
+      </c>
+      <c r="E42" t="inlineStr">
+        <is>
+          <t>sistem penilaian judul tugas akhir berbasis indobert</t>
+        </is>
+      </c>
+      <c r="F42" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G42" t="inlineStr">
+        <is>
+          <t>Cukup Unik</t>
+        </is>
+      </c>
+      <c r="H42" t="inlineStr">
+        <is>
+          <t>klasifikasi judul tugas akhir menggunakan bidirectional long short term memory bilstm pada fakultas teknik universitas nurul jadid</t>
+        </is>
+      </c>
+      <c r="I42" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J42" t="inlineStr">
+        <is>
+          <t>Mirip</t>
+        </is>
+      </c>
+      <c r="K42" t="inlineStr">
+        <is>
+          <t>sistem informasi pencarian judul skripsi berbasis informasi retrival di universitas nurul jadid paiton probolinggo</t>
+        </is>
+      </c>
+      <c r="L42" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M42" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N42" t="inlineStr">
+        <is>
+          <t>pengembangan aplikasi pengajuan judul skripsi di universitas nurul jadid paiton probolinggo berbasis web menggunakan laravel 5 4</t>
+        </is>
+      </c>
+      <c r="O42" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="P42" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q42" t="inlineStr">
+        <is>
+          <t>sistem rekomendasi mata kuliah pilihan menggunakan metode item-based collaborative filtering</t>
+        </is>
+      </c>
+      <c r="R42" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="S42" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T42" t="inlineStr">
+        <is>
+          <t>pengembangan aplikasi karya tulis non-ilmiah mahasiswa universitas nurul jadid berbasis web</t>
+        </is>
+      </c>
+      <c r="U42" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V42" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="43">
+      <c r="A43" t="n">
+        <v>42</v>
+      </c>
+      <c r="B43" s="3" t="n">
+        <v>46198.34313024305</v>
+      </c>
+      <c r="C43" t="inlineStr">
+        <is>
+          <t>deskripsi</t>
+        </is>
+      </c>
+      <c r="D43" t="inlineStr">
+        <is>
+          <t>e-building regristation registrasi pemakaian penyewaan gedung tepatnya di islamic center kraksaan berbasis website ini merupakan sistem informasi yang membantu untuk mengatasi permasalahan pemakaian penyewaan gedung yang terdapat di islamic center permasalahan yang ada pada pemerintahan daerah ini mendatanya masih manual dari pengurus gedung islamic center dan penyewa harus masih ke islamic untuk meminta ijin menyewa gedung dengan adanya sistem ini penyewa dapat mengakses dan menyewa dari luar atau secara online dan juga penyewa bisa mengecek tanggal kapan gedung islamic center itu bisa dipakai sehingga penyewa tidak ragu lagi untuk menyewa gedung islamic center sistem e-building regristation regristasi pemakaian penyewaan gedung islamic center adalah hal yang penting dalam kegiatan acara pernikahan wisuda dan rapat para pejabat dalam era komputerisasi ini bentuk penyajian yang cepat tepat aktual dan akurat sangat diperlukan sehingga informasi melalui komputer sangat dibutuhkan untuk memudahkan pelayanan di setiap bagian yang ada dalam penyewaan gedung dengan masalah diatas maka solusi yang diusulkan adalah dibangun sistem e-building registration registrasi pemakaian penyewaan gedung islamic center berbasis website diharapkan dengan adanya sistem e-building regristation islamic center ini dapat mengatasi permasalahan mengenai menyewa gedung di islamic center fitur fitur user - registrasi anggota - login - lihat jadwal penggunaan gedung - keperluan sewa gedung - lamanya atau waktu sewa gedung - input tanggal - simpan dan tunggu rekomendasi dari admin - cetak bukti jika disetujui - log out fitur fitur admin - login admin - input data pengguna - rekapitulasi daftar penyewa - memberikan rekomendasi disetujui tidak - keterangan - cetak bukti penyewa - laporan penyewaan gedung 1 tanggal awal sampai dengan tanggal akhir 2 cetak -log out</t>
+        </is>
+      </c>
+      <c r="E43" t="inlineStr">
+        <is>
+          <t>e-building regristation registrasi pemakaian penyewaan gedung tepatnya di islamic center kraksaan berbasis website ini merupakan sistem informasi yang membantu untuk mengatasi permasalahan pemakaian penyewaan gedung yang terdapat di islamic center permasalahan yang ada pada pemerintahan daerah ini mendatanya masih manual dari pengurus gedung islamic center dan penyewa harus masih ke islamic untuk meminta ijin menyewa gedung dengan adanya sistem ini penyewa dapat mengakses dan menyewa dari luar atau secara online dan juga penyewa bisa mengecek tanggal kapan gedung islamic center itu bisa dipakai sehingga penyewa tidak ragu lagi untuk menyewa gedung islamic center sistem e-building regristation regristasi pemakaian penyewaan gedung islamic center adalah hal yang penting dalam kegiatan acara pernikahan wisuda dan rapat para pejabat dalam era komputerisasi ini bentuk penyajian yang cepat tepat aktual dan akurat sangat diperlukan sehingga informasi melalui komputer sangat dibutuhkan untuk memudahkan pelayanan di setiap bagian yang ada dalam penyewaan gedung dengan masalah diatas maka solusi yang diusulkan adalah dibangun sistem e-building registration registrasi pemakaian penyewaan gedung islamic center berbasis website diharapkan dengan adanya sistem e-building regristation islamic center ini dapat mengatasi permasalahan mengenai menyewa gedung di islamic center fitur fitur user - registrasi anggota - login - lihat jadwal penggunaan gedung - keperluan sewa gedung - lamanya atau waktu sewa gedung - input tanggal - simpan dan tunggu rekomendasi dari admin - cetak bukti jika disetujui - log out fitur fitur admin - login admin - input data pengguna - rekapitulasi daftar penyewa - memberikan rekomendasi disetujui tidak - keterangan - cetak bukti penyewa - laporan penyewaan gedung 1 tanggal awal sampai dengan tanggal akhir 2 cetak -log out</t>
+        </is>
+      </c>
+      <c r="F43" t="n">
+        <v>1</v>
+      </c>
+      <c r="G43" t="inlineStr">
+        <is>
+          <t>Sangat Unik</t>
+        </is>
+      </c>
+      <c r="H43" t="inlineStr">
+        <is>
+          <t>pondok pesantren nurul jadid sub bagian rumah tangga yang menjadi studi kasus penelitian saat ini masih menggunakan layanan administrasi secara manual sehingga penyewa peminjam sarana dan prasarana masih harus mendatangi kantor sekretariat pondok pesantren nurul jadid sub bagian rumah tangga secara langsung dimana tak jarang para penyewa peminjam sarana dan prasarana mendapati sarana dan prasarana yang ingin ditempati acaranya sudah disewa dipinjam oleh penyewa peminjam sarana dan prasarana yang lain sehingga perlu adanya sebuah peningkatan dalam perihal layanan sistem administrasinya peneliti membuat sebuah sistem peminjaman sarana dan prasarana di pondok pesantren nurul jadid berbasis online menggunakan website dengan adanya sebuah sistem penyewaan peminjaman sarana dan prasarana berbasis online ini diharapkan agar mempermudah alur administrasi bagi penyewa peminjam dan petugas administratif sarana dan prasarana pondok pesantren nurul jadid didalam sistem peminjaman sarana dan prasarana berbasis online ini petugas administratif sarana dan prasarana tidak perlu mendata jadwal peminjaman sarana dan prasarana secara manual dan tidak akan kehilangan data peminjaman sarana dan prasarana sedangkan penyewa peminjam sarana dan prasarana tidak kesulitan dalam proses peminjaman sarana dan prasarana dan tidak akan terjadi dua acara atau lebih yang memakai sarana dan prasarana secara bersamaan</t>
+        </is>
+      </c>
+      <c r="I43" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="J43" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="K43" t="inlineStr">
+        <is>
+          <t>aula di universitas nurul jadid yang menjadi studi kasus penelitian saat ini masih menggunakan layanan administrasi secara manual sehingga peminjam aula masih mendatangi kantor adminitrasi aula secara langsung sering terjadi kesamaan jadwal dalam proses peminjaman tersebut yang disebabkan tidak meluasnya informasi aula yang telah digunakan oleh sebab itu sistem monitoring yang akan dirancang meliputi jadwal pemakaian aula yang dapat dilihat didalam smartphone dan notifikasi terkait peminjam aula jadi bagi yang mau meminjam aula akan mendapatkan notifikasi perihal peminjam aula</t>
+        </is>
+      </c>
+      <c r="L43" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M43" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N43" t="inlineStr">
+        <is>
+          <t>perkembangan ilmu pengetahuan dan teknologi informasi saat ini sudah sangat pesat dari waktu ke waktu ilmu pengetahuan dan teknologi informasi telah mengalami banyak perkembangan dan kemajuan selain sebagai tempat penunjang pendidikan mahasiswa universitas nurul jadid juga mendukung segala aspek kebutuhan-kebutuhan untuk setiap acara diluar perkuliahan mahasiswa salah satu contoh adalah seminar musyawarah besar mubes dan lain lain yang diakanoleh unit kerja seperti ukm dan unit lainnya yang mana harus mengajukan terlebih dahulu surat peminjaman ruang kepada badan pengelola lingkungan kampus bplk salah satu tugas dan fungsinya adalah memberikan pelayanan sarana dan prasarana berupa peminjaman ruangan atau penggunaan izin ruangan untuk menunjang segala kegiatan aktivitas diluar perkuliahan yang ada dilingkungan universitas nurul jadid yang mana ruangan merupakan tempat yang sangat cocok untuk kegiatan internal maupun external peminjaman dimulai dengan mengisi sebuah form yang telah disediakan oleh staff kemudian setelah pengisian form selesai peminjam harus menemui kepala bagian kabag umum bplk untuk meminta persetujuan selain itu untuk acara kegiatan yang menengah dan tidak terlalu besar yang dilakukan oleh unit kegiatan mahasiswa ukm maupun himpunan mahasiswa program studi hmps dan unit lainnya perlu pengajuan surat permohonan yang di serahkan kepada kepala bagian kabag umum bplk untuk meminta persetujuan jika pengajuan surat permohonan itu ditolak maka harus mengajukan permohonan baru dikarenakan mereka peminjam tidak bisa mengecek informasi ruangan yang dipinjam terkecuali melakukan survey terlebih dahulu untuk melihat info ruangan mana yang kosong permasalahan lainnya adalah bagian kabag umum bplk masih harus memeriksa jadwal kegiatan yang berlangsung memeriksa ruangan yang dipinjam tersebut terpakai ataukah tidak terpakai kosong</t>
+        </is>
+      </c>
+      <c r="O43" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="P43" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q43" t="inlineStr">
+        <is>
+          <t>e-marketplace adalah sebuah website atau aplikasi online yang memfasilitasi proses jual beli dari berbagai toko dengan konsep yang kurang lebih sama dengan pasar tradisional m syarif 2020 furniture atau mebel merupakan perabot yang diperlukan berguna atau disukai seperti barang atau benda yang dapat dipindah-pindah digunakan untuk melengkapi rumah kantor dan sebagainya furniture tentu menjadi salah satu aspek paling penting dan diutamakan dalam kehidupan salah satu yang membutuhkan adalah kantor kantor tidak bisa beroperasi jika tidak memiliki furniture sebagai tempat untuk meletakkan dan menyimpan barang furniture yang dibutuhkan oleh sebuah kantor tentu banyak antara lain adalah meja kursi lemari arsip rak buku dan lain-lainnya elisa digna 2020 django adalah web framework berbasis bahasa pemrograman python django adalah web framework python yang didesain untuk membuat aplikasi web yang dinamis kaya fitur dan aman django yang dikembangkan oleh django software foundation terus mendapatkan perbaikan sehingga membuat web framework yang satu ini menjadi pilihan utama bagi banyak pengembang aplikasi web saputra1 aji 2018 lokasi kendit situbondo ud trijuita meubel</t>
+        </is>
+      </c>
+      <c r="R43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="S43" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T43" t="inlineStr">
+        <is>
+          <t>colocation di data center diskominfo adalah layanan untuk menitipkan server fisik milik dinas di luar diskominfo yang mana layanan tersebut disediakan space rack untuk server fisik listrik cooling dan internet oleh diskominfo akan tetapi untuk administrasi server tetap tanggung jawab dinas yang bersangkutan layanan hosting di diskominfo adalah server yang menjadi penyimpanan file atau aset-aset dalam sebuah website atau aplikasi mulai dari template yang digunakan sampai pada file desain masalah penelitian karena sistem layanan teknologi informasi pada diskominfo kab probolinggo belum terdokumentasi secara elektronik dan masih manual menggunakan surat tujuan penelitian untuk menghasilkan tool manajemen layanan dan untuk dokumentasi permohonan layanan hosting colocation yang diharapkan bisa menjadikan solusi untuk permasalahan yang dialami oleh pemerintah manfaatnya untuk memberikan kemudahan dalam pengajuan layanan tik di diskominfo alurnya perangkat daerah mengajukan permohonan hosting colocation kemudian di verifikasi oleh admin diskominfo admin diskominfo meneruskan ke akun tim teknis setelah tim teknis melakukan pengecekan resource maka akan membuat laporan kalau cukup laporannya berisi bahwa bisa di eksekusi tetapi kalau tidak cukup maka akan membuat laporan tidak cukup kalau ada permintaan hosting tim teknis ngecek di server apakah space penyimpanannya masih cukup kalau yang diminta colocation tim teknis akan cek ketersedian rak internet dan listrik aplikasi ini akan memiliki beberapa fitur yaitu grafik data master admin register tabel hak akses ketika login user ada pemohon ada 2 menu tetapi beda menu yaitu menu hosting dan colocation ada pimpinan ada pejabat teknis ada teknis ada administrator di menu permohonan hosting ada nama domain jenis domain versi php php extention database storage shell acces yes no pic penanggung jawab no pic no penanggung jawab upload surat berbentuk pdf di menu colocation ada merk server type server jumlah core jumlah ram jumlah hardisk pic penanggung jawab no pic no penanggung jawab upload surat berbentuk pdf di menu pimpinan ada grafik dimana untuk mengetahui status historinya yaitu ada 0 belum di disposisi 1 sudah di disposisi ke pejabat teknis 2 sudah dilaksanakan oleh pelaksana teknis 3 respon informasi akun sudah di sampaikan ke pemohon selesai</t>
+        </is>
+      </c>
+      <c r="U43" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V43" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="44">
+      <c r="A44" t="n">
+        <v>43</v>
+      </c>
+      <c r="B44" s="3" t="n">
+        <v>46198.34408024306</v>
+      </c>
+      <c r="C44" t="inlineStr">
+        <is>
+          <t>kombinasi</t>
+        </is>
+      </c>
+      <c r="D44" t="inlineStr">
+        <is>
+          <t>rancang bangun sistem pemetaan geografis rawan kecelakaan atau perampok di desa wangkal berbasis web desa wangkal memiliki banyak penduduk dalam hal ini sering kali kepala desa atau penduduk mendapatkan informasi kecelakaan di desa wangkal seringkali dari setiap tempat sudah dipahami oleh penduduk setempat yang seringkali terjadi kecelakaan dan petugas desa kesulitan untuk mencatat lokasi-lokasi yang sering kali terjadi kecelakaan sehingga tidak dapat memberikan tanda bahaya di tempat lokasi tersebut dengan sering terjadinya kecelakaan kepala desa kesulitan untuk melaporkan ke polisi dengan tujuan memberikan tanda peringatan tiap-tiap lokasi yang sering terjadi kecelakaan maka dari itu desa wangkal membutuhkan sistem yang dapat memberikan tanda yang sering terjadi kecelakaan di desa wangkal</t>
+        </is>
+      </c>
+      <c r="E44" t="inlineStr">
+        <is>
+          <t>rancang bangun sistem pemetaan geografis rawan kecelakaan atau perampok di desa wangkal berbasis web desa wangkal memiliki banyak penduduk dalam hal ini sering kali kepala desa atau penduduk mendapatkan informasi kecelakaan di desa wangkal seringkali dari setiap tempat sudah dipahami oleh penduduk setempat yang seringkali terjadi kecelakaan dan petugas desa kesulitan untuk mencatat lokasi-lokasi yang sering kali terjadi kecelakaan sehingga tidak dapat memberikan tanda bahaya di tempat lokasi tersebut dengan sering terjadinya kecelakaan kepala desa kesulitan untuk melaporkan ke polisi dengan tujuan memberikan tanda peringatan tiap-tiap lokasi yang sering terjadi kecelakaan maka dari itu desa wangkal membutuhkan sistem yang dapat memberikan tanda yang sering terjadi kecelakaan di desa wangkal</t>
+        </is>
+      </c>
+      <c r="F44" t="n">
+        <v>1</v>
+      </c>
+      <c r="G44" t="inlineStr">
+        <is>
+          <t>Sangat Unik</t>
+        </is>
+      </c>
+      <c r="H44" t="inlineStr">
+        <is>
+          <t>sistem informasi desa alasnyiur berbasis web menggunakan framework laravel deskripsi dari judul sistem informasi desa alasnyiur berbasis web menggunakan framework laravel adalah sebagai berikut judul tersebut mencerminkan pembangunan sistem informasi yang ditujukan khusus untuk desa alasnyiur dengan pendekatan berbasis web sistem ini akan dirancang dan dikembangkan menggunakan framework laravel sebuah framework php modern yang memungkinkan pengembangan aplikasi web yang efisien dan skalabel dengan menggunakan laravel sistem ini akan memiliki keunggulan dalam hal keamanan kinerja serta kemudahan dalam integrasi dengan berbagai komponen teknologi modern lainnya tujuan utama dari sistem ini adalah untuk meningkatkan efektivitas dan efisiensi pengelolaan informasi pelayanan kepada masyarakat serta administrasi desa secara keseluruhan di desa alasnyiur</t>
+        </is>
+      </c>
+      <c r="I44" t="n">
+        <v>0.6</v>
+      </c>
+      <c r="J44" t="inlineStr">
+        <is>
+          <t>Mirip</t>
+        </is>
+      </c>
+      <c r="K44" t="inlineStr">
+        <is>
+          <t>sistem informasi pelayanan surat dan pengaduan masyarakat di desa wangkal menggunakan framework laravel sistem informasi pelayanan surat dan pengaduan masyarakat di desa wangkal menggunakan framework laravel adalah sebuah aplikasi berbasis web yang dirancang untuk membantu pemerintah desa dalam mengelola pelayanan surat dan pengaduan masyarakat sistem ini dapat membantu meningkatkan efisiensi transparansi dan akuntabilitas pelayanan publik di desa</t>
+        </is>
+      </c>
+      <c r="L44" t="n">
+        <v>0.59</v>
+      </c>
+      <c r="M44" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N44" t="inlineStr">
+        <is>
+          <t>sistem informasi pengaduan masyarakat pemerintahan desa pasembon menggunakan notifikasi via whatsapp otomatis pemerintahan pasembon merupakan pemerintahan yang berada di daerah pelosokan yang menjadi pusat pelayanan bagi masyarakat dalam tingkat pedasaan pusat pelayanan menjadi kebutuhan masyarakat dalam mengurus data data bansos dan sesuai kebutuhan yang diinginkan terdapat beberapa permasalahan dalam pemerintahan yang pertama yaitu minimnya penyebaran sistem informasi meliputi program kerja fasilitas anggaran desa dan penerimaan bansos sehingga menyebabkan terjadinya perbincangan oleh masyarakat karena sistem informasi pemerintahan desa yang belum diketahui dalam hal ini misalnya sistem informasi penyaluran bantuan sosial yang kedua yaitu kurangnya respon pemerintahan dalam menjawab pertanyaan tujuan dibuatnya sistem informasi dan pengaduan pemerintahan desa pasembon adalah untuk mempermudah masyarakat dalam mengetahui informasi yang dapat diakses melalui website dan memberikan pelayanan pengaduan yang telah di ajukan oleh masyarakat melalui fitur via whatsapp yang nantinya akan mendapatkan notifikasi secara otomatis</t>
+        </is>
+      </c>
+      <c r="O44" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="P44" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q44" t="inlineStr">
+        <is>
+          <t>pemetaan masyarakan di desa alastengah menggunakan gis pemetaan masyarakat di desa alastengah adalah upaya yang di lakukan untuk melihat besarnya masalah serta penentuan program dan tujuan penelitian untuk mengetahui gambaran umum kondisi masyarakat potensi masalah dan kebutuhan yang ada pada lingkupan social permasalahnnya seperti masyarakat masih menggunakan sungai untuk aktifitas mandi cuci baju dan lain lain dengan sebab itu dengan adanya pemetaan masyarakat di desa alastengah menggunakan gis ini bisa mengetahui data data masyarakat mana masyarakat yang kurang mampu atau masyarakat yang sudah mampu</t>
+        </is>
+      </c>
+      <c r="R44" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="S44" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T44" t="inlineStr">
+        <is>
+          <t>sistem informasi monitoring pindah penduduk dan datang penduduk di kantor desa paiton berbasis web perkembangan teknologi yang sangat cepat senantiasa menuntut kita dan perusahaan untuk melakukan perubahan dalam proses bisnis internal yang sedang berjalan saat ini hadirnya teknologi informasi saat ini dapat berlangsung secara berkesinambungan pada dekade terakhir dan telah meningkatkan efektifitas dan efisiensi dari proses bisnis yang ada secara signifikan kantor desa paiton bergerak di bidang pelayanan masyarakat kantor desa paiton selalu siap melayani apa saja yang dibutuhkan oleh masyarakat umum lainnya seperti pembuatan surat pindah datang penduduk melihat dari kondisi yang ada saat ini sistem informasi pelayanan yang dilakukan di kantor desa paiton masih belum maksimal dimana proses pengolahan data layanan surat pindah penduduk masih menggunakan manual kesulitan dalam mengecek data penduduk dan kepindahan penduduk proses pembuatan laporan masih menggunakan word dan excel tetapi itu belum maksimal untuk mengatasi permasalahan yang ada terjadi penumpukan arsip yang tidak teratur karna belum tersedianya tempat penyimpanan arsip yang baik sehingga waktu yang banyak terbuang dan keamanan datapun jadi kurang terjamin di bagian pelayanan belum mengadakan sistem untuk mengolah data penduduk berdasarkan deskripsi yang peneliti paparkan diatas peneliti ingin memudahkan pihak kantor desa paiton untuk melayani masyarakat dalam pembuatan surat pindah penduduk dan datang penduduk yang akan terkomputerisasi sehingga pihak kantor desa paiton tidak akan kesulitan lagi dalam pembuatan surat pindah penduduk dan datang penduduk</t>
+        </is>
+      </c>
+      <c r="U44" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="V44" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="W44" t="inlineStr">
+        <is>
+          <t>rancang bangun sistem pemetaan geografis rawan kecelakaan atau perampok di desa wangkal berbasis web</t>
+        </is>
+      </c>
+      <c r="X44" t="inlineStr">
+        <is>
+          <t>desa wangkal memiliki banyak penduduk dalam hal ini sering kali kepala desa atau penduduk mendapatkan informasi kecelakaan di desa wangkal seringkali dari setiap tempat sudah dipahami oleh penduduk setempat yang seringkali terjadi kecelakaan dan petugas desa kesulitan untuk mencatat lokasi-lokasi yang sering kali terjadi kecelakaan sehingga tidak dapat memberikan tanda bahaya di tempat lokasi tersebut dengan sering terjadinya kecelakaan kepala desa kesulitan untuk melaporkan ke polisi dengan tujuan memberikan tanda peringatan tiap-tiap lokasi yang sering terjadi kecelakaan maka dari itu desa wangkal membutuhkan sistem yang dapat memberikan tanda yang sering terjadi kecelakaan di desa wangkal</t>
+        </is>
+      </c>
+      <c r="Y44" t="inlineStr">
+        <is>
+          <t>sistem informasi desa alasnyiur berbasis web menggunakan framework laravel</t>
+        </is>
+      </c>
+      <c r="Z44" t="inlineStr">
+        <is>
+          <t>deskripsi dari judul sistem informasi desa alasnyiur berbasis web menggunakan framework laravel adalah sebagai berikut judul tersebut mencerminkan pembangunan sistem informasi yang ditujukan khusus untuk desa alasnyiur dengan pendekatan berbasis web sistem ini akan dirancang dan dikembangkan menggunakan framework laravel sebuah framework php modern yang memungkinkan pengembangan aplikasi web yang efisien dan skalabel dengan menggunakan laravel sistem ini akan memiliki keunggulan dalam hal keamanan kinerja serta kemudahan dalam integrasi dengan berbagai komponen teknologi modern lainnya tujuan utama dari sistem ini adalah untuk meningkatkan efektivitas dan efisiensi pengelolaan informasi pelayanan kepada masyarakat serta administrasi desa secara keseluruhan di desa alasnyiur</t>
+        </is>
+      </c>
+      <c r="AA44" t="inlineStr">
+        <is>
+          <t>sistem informasi pelayanan surat dan pengaduan masyarakat di desa wangkal menggunakan framework laravel</t>
+        </is>
+      </c>
+      <c r="AB44" t="inlineStr">
+        <is>
+          <t>sistem informasi pelayanan surat dan pengaduan masyarakat di desa wangkal menggunakan framework laravel adalah sebuah aplikasi berbasis web yang dirancang untuk membantu pemerintah desa dalam mengelola pelayanan surat dan pengaduan masyarakat sistem ini dapat membantu meningkatkan efisiensi transparansi dan akuntabilitas pelayanan publik di desa</t>
+        </is>
+      </c>
+      <c r="AC44" t="inlineStr">
+        <is>
+          <t>sistem informasi pengaduan masyarakat pemerintahan desa pasembon menggunakan notifikasi via whatsapp otomatis</t>
+        </is>
+      </c>
+      <c r="AD44" t="inlineStr">
+        <is>
+          <t>pemerintahan pasembon merupakan pemerintahan yang berada di daerah pelosokan yang menjadi pusat pelayanan bagi masyarakat dalam tingkat pedasaan pusat pelayanan menjadi kebutuhan masyarakat dalam mengurus data data bansos dan sesuai kebutuhan yang diinginkan terdapat beberapa permasalahan dalam pemerintahan yang pertama yaitu minimnya penyebaran sistem informasi meliputi program kerja fasilitas anggaran desa dan penerimaan bansos sehingga menyebabkan terjadinya perbincangan oleh masyarakat karena sistem informasi pemerintahan desa yang belum diketahui dalam hal ini misalnya sistem informasi penyaluran bantuan sosial yang kedua yaitu kurangnya respon pemerintahan dalam menjawab pertanyaan tujuan dibuatnya sistem informasi dan pengaduan pemerintahan desa pasembon adalah untuk mempermudah masyarakat dalam mengetahui informasi yang dapat diakses melalui website dan memberikan pelayanan pengaduan yang telah di ajukan oleh masyarakat melalui fitur via whatsapp yang nantinya akan mendapatkan notifikasi secara otomatis</t>
+        </is>
+      </c>
+      <c r="AE44" t="inlineStr">
+        <is>
+          <t>pemetaan masyarakan di desa alastengah menggunakan gis</t>
+        </is>
+      </c>
+      <c r="AF44" t="inlineStr">
+        <is>
+          <t>pemetaan masyarakat di desa alastengah adalah upaya yang di lakukan untuk melihat besarnya masalah serta penentuan program dan tujuan penelitian untuk mengetahui gambaran umum kondisi masyarakat potensi masalah dan kebutuhan yang ada pada lingkupan social permasalahnnya seperti masyarakat masih menggunakan sungai untuk aktifitas mandi cuci baju dan lain lain dengan sebab itu dengan adanya pemetaan masyarakat di desa alastengah menggunakan gis ini bisa mengetahui data data masyarakat mana masyarakat yang kurang mampu atau masyarakat yang sudah mampu</t>
+        </is>
+      </c>
+      <c r="AG44" t="inlineStr">
+        <is>
+          <t>sistem informasi monitoring pindah penduduk dan datang penduduk di kantor desa paiton berbasis web</t>
+        </is>
+      </c>
+      <c r="AH44" t="inlineStr">
+        <is>
+          <t>perkembangan teknologi yang sangat cepat senantiasa menuntut kita dan perusahaan untuk melakukan perubahan dalam proses bisnis internal yang sedang berjalan saat ini hadirnya teknologi informasi saat ini dapat berlangsung secara berkesinambungan pada dekade terakhir dan telah meningkatkan efektifitas dan efisiensi dari proses bisnis yang ada secara signifikan kantor desa paiton bergerak di bidang pelayanan masyarakat kantor desa paiton selalu siap melayani apa saja yang dibutuhkan oleh masyarakat umum lainnya seperti pembuatan surat pindah datang penduduk melihat dari kondisi yang ada saat ini sistem informasi pelayanan yang dilakukan di kantor desa paiton masih belum maksimal dimana proses pengolahan data layanan surat pindah penduduk masih menggunakan manual kesulitan dalam mengecek data penduduk dan kepindahan penduduk proses pembuatan laporan masih menggunakan word dan excel tetapi itu belum maksimal untuk mengatasi permasalahan yang ada terjadi penumpukan arsip yang tidak teratur karna belum tersedianya tempat penyimpanan arsip yang baik sehingga waktu yang banyak terbuang dan keamanan datapun jadi kurang terjamin di bagian pelayanan belum mengadakan sistem untuk mengolah data penduduk berdasarkan deskripsi yang peneliti paparkan diatas peneliti ingin memudahkan pihak kantor desa paiton untuk melayani masyarakat dalam pembuatan surat pindah penduduk dan datang penduduk yang akan terkomputerisasi sehingga pihak kantor desa paiton tidak akan kesulitan lagi dalam pembuatan surat pindah penduduk dan datang penduduk</t>
+        </is>
+      </c>
+    </row>
+    <row r="45">
+      <c r="A45" t="n">
+        <v>44</v>
+      </c>
+      <c r="B45" s="3" t="n">
+        <v>46200.32954807871</v>
+      </c>
+      <c r="C45" t="inlineStr">
+        <is>
+          <t>judul</t>
+        </is>
+      </c>
+      <c r="D45" t="inlineStr">
+        <is>
+          <t>dengan menggunakan konsep jaringan internet of things kita dapat membuat sebuah sistem yang bisa memantau infus pada pasien sensor yang di gunakan adalah sensor load cell untuk mendeteksi volume infus pada botol serta menggunakan led super bright dan photodiode yang di pasang pada drip chamber sebagai indikator yang akan mendeteksi infus menetes ketika cairan akan habis maka sensor akan memberikan pesan telegram yang masuk pada smart phone android perawat yang bertugas serta menggunakan sensor warna tcs 34725 rgb sensor untuk mendeteksi darah yang naik pada alliran selang infus yang dapat membekukan aliran infus pada selang</t>
+        </is>
+      </c>
+      <c r="E45" t="inlineStr">
+        <is>
+          <t>dengan menggunakan konsep jaringan internet of things kita dapat membuat sebuah sistem yang bisa memantau infus pada pasien sensor yang di gunakan adalah sensor load cell untuk mendeteksi volume infus pada botol serta menggunakan led super bright dan photodiode yang di pasang pada drip chamber sebagai indikator yang akan mendeteksi infus menetes ketika cairan akan habis maka sensor akan memberikan pesan telegram yang masuk pada smart phone android perawat yang bertugas serta menggunakan sensor warna tcs 34725 rgb sensor untuk mendeteksi darah yang naik pada alliran selang infus yang dapat membekukan aliran infus pada selang</t>
+        </is>
+      </c>
+      <c r="F45" t="n">
+        <v>1</v>
+      </c>
+      <c r="G45" t="inlineStr">
+        <is>
+          <t>Sangat Unik</t>
+        </is>
+      </c>
+      <c r="H45" t="inlineStr">
+        <is>
+          <t>monitoring infus dan pulse heart rate berbasis iot</t>
+        </is>
+      </c>
+      <c r="I45" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J45" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="K45" t="inlineStr">
+        <is>
+          <t>prototipe water filing system pada produksi air dalam kemasan mengunakan flow sensor berbasis mikrokontroler atmega 16</t>
+        </is>
+      </c>
+      <c r="L45" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="M45" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N45" t="inlineStr">
+        <is>
+          <t>aplikasi sensor tekanan pada tabung oksigen berbasis iot di rumah sakit waluyo jati menggunakan hp android</t>
+        </is>
+      </c>
+      <c r="O45" t="n">
+        <v>0.55</v>
+      </c>
+      <c r="P45" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q45" t="inlineStr">
+        <is>
+          <t>perancangan kontrol temperature thermoelectric cooler menggunakan kontrol pid pada directional bucket air counditioner</t>
+        </is>
+      </c>
+      <c r="R45" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="S45" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T45" t="inlineStr">
+        <is>
+          <t>rekam data self manajemen cairan pada pasien gagal ginjal kronis yang menjalani terapi hemodialisa di rsud abdoer rahem berbasis android</t>
+        </is>
+      </c>
+      <c r="U45" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="V45" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="46">
+      <c r="A46" t="n">
+        <v>45</v>
+      </c>
+      <c r="B46" s="3" t="n">
+        <v>46200.33037482639</v>
+      </c>
+      <c r="C46" t="inlineStr">
+        <is>
+          <t>deskripsi</t>
+        </is>
+      </c>
+      <c r="D46" t="inlineStr">
+        <is>
+          <t>monitoring infus dan pulse heart rate berbasis iot</t>
+        </is>
+      </c>
+      <c r="E46" t="inlineStr">
+        <is>
+          <t>monitoring infus dan pulse heart rate berbasis iot</t>
+        </is>
+      </c>
+      <c r="F46" t="n">
+        <v>1</v>
+      </c>
+      <c r="G46" t="inlineStr">
+        <is>
+          <t>Sangat Unik</t>
+        </is>
+      </c>
+      <c r="H46" t="inlineStr">
+        <is>
+          <t>alat ini digunakan untuk memonitoring kesehatan masyarakat terutama penyakit jantung dan suhu tubuh kurangnya ketersediaan alat pada puskesmas desa gondosuli menjadi salah satu alasan terciptanya alat pendeteksi detak jantung dan suhu tubuh berbasis iot ini</t>
+        </is>
+      </c>
+      <c r="I46" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="J46" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="K46" t="inlineStr">
+        <is>
+          <t>dengan menggunakan konsep jaringan internet of things kita dapat membuat sebuah sistem yang bisa memantau infus pada pasien sensor yang di gunakan adalah sensor load cell untuk mendeteksi volume infus pada botol serta menggunakan led super bright dan photodiode yang di pasang pada drip chamber sebagai indikator yang akan mendeteksi infus menetes ketika cairan akan habis maka sensor akan memberikan pesan telegram yang masuk pada smart phone android perawat yang bertugas serta menggunakan sensor warna tcs 34725 rgb sensor untuk mendeteksi darah yang naik pada alliran selang infus yang dapat membekukan aliran infus pada selang</t>
+        </is>
+      </c>
+      <c r="L46" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="M46" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N46" t="inlineStr">
+        <is>
+          <t>penelitan ini dilakukan berlandaskan dari penelitian sebelumnya yang menjelaskan bahwa untuk meningkatkan self manajemen dalam melakukan pembatasan asupan cairan pada pasien gagal ginjal kronis salah satunya dengan cara menggunakan alat pengontrol asupan cairan menggunakan aplikasi android hal ini sesuai dengan hasil wawancara yang dilakukan dengan perawat kepala ruang hemodialisa bahwasannya terdapat permasalahan di ruang terapi hemodialisa yaitu sering didapatkan kelebihan cairan pada saat di lakukan tindakan hemodialisa pada pasien gagal ginjal kronis hal ini dikarenakan belum adanya metode yang dapat meningkatkan manajemen diri dalam melakukan pembatasan asupan cairan pada pasien gagal ginjal kronis sulit untuk mengetahui apakah asupan cairan yang di konsumsi telah mencapai batas asupan cairan yang telah ditentukan oleh dokter atau tidak selain itu pasien juga sering lupa terhadap jumlah asupan cairan yang sudah di konsumsi salah satu penderita gagal ginjal kronis yang menjalani terapi di ruang hemodialisa dari paparan diatas penelitian ini diusulkan menggunakan aplikasi berbasis android yang memudahkan pasien untuk mengakses informasi mengenai gagal ginjal kronis selain sistem informasi aplikasi ini memiliki beberapa fitur seperti perhitungan intake output cairan reminder harian grafik untuk menggambarkan data perkembangan dan perbandingan informasi secara jelas dengan aplikasi android ini diharapkan dapat meningkatkan manejemen diri pada pasien gagal ginjal kronis dalam melakukan pembatasan asupan cairan sehingga dapat memudahkan pasien dalam pengontrolan cairan</t>
+        </is>
+      </c>
+      <c r="O46" t="n">
+        <v>0.5600000000000001</v>
+      </c>
+      <c r="P46" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q46" t="inlineStr">
+        <is>
+          <t>aplikasi menggunakan sensor tekanan pada tabung oksigen berbasis iot ini memudahkan dokter dan perawat di rsud waluyo jati mempercepat pekerjaan karena data mengenai berkurangnya isi pada tabung oksigen ini langsung secara otomatis mengirimkan notifikasi ke hp android karena sampai saat ini masih menggunakan pressure indicator air</t>
+        </is>
+      </c>
+      <c r="R46" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="S46" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T46" t="inlineStr">
+        <is>
+          <t>rancang bangun monitoring pengisian baterai speda listrik berbasis internet of thing iot</t>
+        </is>
+      </c>
+      <c r="U46" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="V46" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="47">
+      <c r="A47" t="n">
+        <v>46</v>
+      </c>
+      <c r="B47" s="3" t="n">
+        <v>46200.60459131945</v>
+      </c>
+      <c r="C47" t="inlineStr">
+        <is>
+          <t>judul</t>
+        </is>
+      </c>
+      <c r="D47" t="inlineStr">
+        <is>
+          <t>Sistem Penilaian Judul Tugas Akhir Berbasis Indobert</t>
+        </is>
+      </c>
+      <c r="E47" t="inlineStr">
+        <is>
+          <t>sistem penilaian judul tugas akhir berbasis indobert</t>
+        </is>
+      </c>
+      <c r="F47" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G47" t="inlineStr">
+        <is>
+          <t>Cukup Unik</t>
+        </is>
+      </c>
+      <c r="H47" t="inlineStr">
+        <is>
+          <t>klasifikasi judul tugas akhir menggunakan bidirectional long short term memory bilstm pada fakultas teknik universitas nurul jadid</t>
+        </is>
+      </c>
+      <c r="I47" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J47" t="inlineStr">
+        <is>
+          <t>Mirip</t>
+        </is>
+      </c>
+      <c r="K47" t="inlineStr">
+        <is>
+          <t>sistem informasi pencarian judul skripsi berbasis informasi retrival di universitas nurul jadid paiton probolinggo</t>
+        </is>
+      </c>
+      <c r="L47" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M47" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N47" t="inlineStr">
+        <is>
+          <t>pengembangan aplikasi pengajuan judul skripsi di universitas nurul jadid paiton probolinggo berbasis web menggunakan laravel 5 4</t>
+        </is>
+      </c>
+      <c r="O47" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="P47" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q47" t="inlineStr">
+        <is>
+          <t>sistem rekomendasi mata kuliah pilihan menggunakan metode item-based collaborative filtering</t>
+        </is>
+      </c>
+      <c r="R47" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="S47" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T47" t="inlineStr">
+        <is>
+          <t>pengembangan aplikasi karya tulis non-ilmiah mahasiswa universitas nurul jadid berbasis web</t>
+        </is>
+      </c>
+      <c r="U47" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V47" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="48">
+      <c r="A48" t="n">
+        <v>47</v>
+      </c>
+      <c r="B48" s="3" t="n">
+        <v>46200.60922716435</v>
+      </c>
+      <c r="C48" t="inlineStr">
+        <is>
+          <t>deskripsi</t>
+        </is>
+      </c>
+      <c r="D48" t="inlineStr">
+        <is>
+          <t>alat ini berguna untuk memantau cairan infus yang ada di klinik azzaniyah nurul jadid seningga memudahkan suster atau dokter memantau cairan infus agar tidak sampai bener benar habis seningga menghambat proses penyembuhan</t>
+        </is>
+      </c>
+      <c r="E48" t="inlineStr">
+        <is>
+          <t>alat ini berguna untuk memantau cairan infus yang ada di klinik azzaniyah nurul jadid seningga memudahkan suster atau dokter memantau cairan infus agar tidak sampai bener benar habis seningga menghambat proses penyembuhan</t>
+        </is>
+      </c>
+      <c r="F48" t="n">
+        <v>0.58</v>
+      </c>
+      <c r="G48" t="inlineStr">
+        <is>
+          <t>Cukup Unik</t>
+        </is>
+      </c>
+      <c r="H48" t="inlineStr">
+        <is>
+          <t>dengan menggunakan konsep jaringan internet of things kita dapat membuat sebuah sistem yang bisa memantau infus pada pasien sensor yang di gunakan adalah sensor load cell untuk mendeteksi volume infus pada botol serta menggunakan led super bright dan photodiode yang di pasang pada drip chamber sebagai indikator yang akan mendeteksi infus menetes ketika cairan akan habis maka sensor akan memberikan pesan telegram yang masuk pada smart phone android perawat yang bertugas serta menggunakan sensor warna tcs 34725 rgb sensor untuk mendeteksi darah yang naik pada alliran selang infus yang dapat membekukan aliran infus pada selang</t>
+        </is>
+      </c>
+      <c r="I48" t="n">
+        <v>0.77</v>
+      </c>
+      <c r="J48" t="inlineStr">
+        <is>
+          <t>Mirip</t>
+        </is>
+      </c>
+      <c r="K48" t="inlineStr">
+        <is>
+          <t>aplikasi menggunakan sensor tekanan pada tabung oksigen berbasis iot ini memudahkan dokter dan perawat di rsud waluyo jati mempercepat pekerjaan karena data mengenai berkurangnya isi pada tabung oksigen ini langsung secara otomatis mengirimkan notifikasi ke hp android karena sampai saat ini masih menggunakan pressure indicator air</t>
+        </is>
+      </c>
+      <c r="L48" t="n">
+        <v>0.53</v>
+      </c>
+      <c r="M48" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N48" t="inlineStr">
+        <is>
+          <t>alat ini dibuat berdasarkan latar belakang permasalahan yang ada pada lingkungan sekitar pondok pesantren nurul jadid salah satunya ialah kurangnya perawatan air sehingga air tercemar limbah berbau berwarna beracun 3b pada bak mandi yang mengakibatkan timbulnya penyakit kulit dan menjadi sarang nyamuk yang dapat menimbulkan berbagai penyakit maka dengan adanya alat yang kami rancang ini dapat membantu dalam masalah perawatan air 3b</t>
+        </is>
+      </c>
+      <c r="O48" t="n">
+        <v>0.44</v>
+      </c>
+      <c r="P48" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q48" t="inlineStr">
+        <is>
+          <t>klinik az-zainiyah adalah sebuah instansi kesehatan yang berada dibawah naungan pondok pesantren nurul jadid yang memiliki fungsi untuk mengurus dan mengobati pasien untuk melakukan pemeriksaan kesehatan dengan fasilitas medis yang sudah disediakan yang mereka layani selama 24 jam dengan beberapa kendala penyakit kesehatan yang mereka alami selain fasilitas medis ada hal lain yang menunjang terbentuknya sisten yang baik yaitu administrasi yang menjadi faktor dalam pencitraan sebuah klinik mengotimalkan pendataan pasien untuk menciptakan sebuah data yang cepat dan akurat dengan meminimalisir proses yang lama untuk memaksimalkan pelayanan terutama terutama peberitahuan wali santri agar mereka mengetahui situasi anaknya jika dalam keadaan sakit dengan adanya sistem tersebut maka akan terbentuknya sumber daya manusia dengan kinerja yang lebih baik sesuai dengan yang diinginkan santri dan pesantren jadi sistem ini dibuat untuk memudahkan wali asuh santri untuk mendaftarkan anak asuhnya ketika sedang sakit sehingga memudahkan klinik untuk melakukan penjemputan pasien ke daerah masing-masing santri</t>
+        </is>
+      </c>
+      <c r="R48" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="S48" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T48" t="inlineStr">
+        <is>
+          <t>penelitan ini dilakukan berlandaskan dari penelitian sebelumnya yang menjelaskan bahwa untuk meningkatkan self manajemen dalam melakukan pembatasan asupan cairan pada pasien gagal ginjal kronis salah satunya dengan cara menggunakan alat pengontrol asupan cairan menggunakan aplikasi android hal ini sesuai dengan hasil wawancara yang dilakukan dengan perawat kepala ruang hemodialisa bahwasannya terdapat permasalahan di ruang terapi hemodialisa yaitu sering didapatkan kelebihan cairan pada saat di lakukan tindakan hemodialisa pada pasien gagal ginjal kronis hal ini dikarenakan belum adanya metode yang dapat meningkatkan manajemen diri dalam melakukan pembatasan asupan cairan pada pasien gagal ginjal kronis sulit untuk mengetahui apakah asupan cairan yang di konsumsi telah mencapai batas asupan cairan yang telah ditentukan oleh dokter atau tidak selain itu pasien juga sering lupa terhadap jumlah asupan cairan yang sudah di konsumsi salah satu penderita gagal ginjal kronis yang menjalani terapi di ruang hemodialisa dari paparan diatas penelitian ini diusulkan menggunakan aplikasi berbasis android yang memudahkan pasien untuk mengakses informasi mengenai gagal ginjal kronis selain sistem informasi aplikasi ini memiliki beberapa fitur seperti perhitungan intake output cairan reminder harian grafik untuk menggambarkan data perkembangan dan perbandingan informasi secara jelas dengan aplikasi android ini diharapkan dapat meningkatkan manejemen diri pada pasien gagal ginjal kronis dalam melakukan pembatasan asupan cairan sehingga dapat memudahkan pasien dalam pengontrolan cairan</t>
+        </is>
+      </c>
+      <c r="U48" t="n">
+        <v>0.43</v>
+      </c>
+      <c r="V48" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+    </row>
+    <row r="49">
+      <c r="A49" t="n">
+        <v>48</v>
+      </c>
+      <c r="B49" s="3" t="n">
+        <v>46200.60961189815</v>
+      </c>
+      <c r="C49" t="inlineStr">
+        <is>
+          <t>kombinasi</t>
+        </is>
+      </c>
+      <c r="D49" t="inlineStr">
+        <is>
+          <t>rancang bangun pemantau berkurangnya cairan infus berbasis arduino dan iot klinik azzaniyah nurul jadid alat ini berguna untuk memantau cairan infus yang ada di klinik azzaniyah nurul jadid seningga memudahkan suster atau dokter memantau cairan infus agar tidak sampai bener benar habis seningga menghambat proses penyembuhan</t>
+        </is>
+      </c>
+      <c r="E49" t="inlineStr">
+        <is>
+          <t>rancang bangun pemantau berkurangnya cairan infus berbasis arduino dan iot klinik azzaniyah nurul jadid alat ini berguna untuk memantau cairan infus yang ada di klinik azzaniyah nurul jadid seningga memudahkan suster atau dokter memantau cairan infus agar tidak sampai bener benar habis seningga menghambat proses penyembuhan</t>
+        </is>
+      </c>
+      <c r="F49" t="n">
+        <v>0.62</v>
+      </c>
+      <c r="G49" t="inlineStr">
+        <is>
+          <t>Cukup Unik</t>
+        </is>
+      </c>
+      <c r="H49" t="inlineStr">
+        <is>
+          <t>monitoring infus dan pulse heart rate berbasis iot dengan menggunakan konsep jaringan internet of things kita dapat membuat sebuah sistem yang bisa memantau infus pada pasien sensor yang di gunakan adalah sensor load cell untuk mendeteksi volume infus pada botol serta menggunakan led super bright dan photodiode yang di pasang pada drip chamber sebagai indikator yang akan mendeteksi infus menetes ketika cairan akan habis maka sensor akan memberikan pesan telegram yang masuk pada smart phone android perawat yang bertugas serta menggunakan sensor warna tcs 34725 rgb sensor untuk mendeteksi darah yang naik pada alliran selang infus yang dapat membekukan aliran infus pada selang</t>
+        </is>
+      </c>
+      <c r="I49" t="n">
+        <v>0.75</v>
+      </c>
+      <c r="J49" t="inlineStr">
+        <is>
+          <t>Mirip</t>
+        </is>
+      </c>
+      <c r="K49" t="inlineStr">
+        <is>
+          <t>aplikasi sensor tekanan pada tabung oksigen berbasis iot di rumah sakit waluyo jati menggunakan hp android aplikasi menggunakan sensor tekanan pada tabung oksigen berbasis iot ini memudahkan dokter dan perawat di rsud waluyo jati mempercepat pekerjaan karena data mengenai berkurangnya isi pada tabung oksigen ini langsung secara otomatis mengirimkan notifikasi ke hp android karena sampai saat ini masih menggunakan pressure indicator air</t>
+        </is>
+      </c>
+      <c r="L49" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="M49" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N49" t="inlineStr">
+        <is>
+          <t>rancang bangun sistem pengendalian persediaan air pada tandon berbasis internet of things iot untuk paseban sena hotel rancang bangun monitoring system otomasi water level tank dan water pump untuk gedung paseban sena hotel adalah peralatan yang menggunakan system internet of think sebagai landasan untuk mempermudah perawatan jika terjadi trobleshoting pada system manual ataupun otomatis level air tendon pompa air listrik</t>
+        </is>
+      </c>
+      <c r="O49" t="n">
+        <v>0.52</v>
+      </c>
+      <c r="P49" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q49" t="inlineStr">
+        <is>
+          <t>rekam data self manajemen cairan pada pasien gagal ginjal kronis yang menjalani terapi hemodialisa di rsud abdoer rahem berbasis android penelitan ini dilakukan berlandaskan dari penelitian sebelumnya yang menjelaskan bahwa untuk meningkatkan self manajemen dalam melakukan pembatasan asupan cairan pada pasien gagal ginjal kronis salah satunya dengan cara menggunakan alat pengontrol asupan cairan menggunakan aplikasi android hal ini sesuai dengan hasil wawancara yang dilakukan dengan perawat kepala ruang hemodialisa bahwasannya terdapat permasalahan di ruang terapi hemodialisa yaitu sering didapatkan kelebihan cairan pada saat di lakukan tindakan hemodialisa pada pasien gagal ginjal kronis hal ini dikarenakan belum adanya metode yang dapat meningkatkan manajemen diri dalam melakukan pembatasan asupan cairan pada pasien gagal ginjal kronis sulit untuk mengetahui apakah asupan cairan yang di konsumsi telah mencapai batas asupan cairan yang telah ditentukan oleh dokter atau tidak selain itu pasien juga sering lupa terhadap jumlah asupan cairan yang sudah di konsumsi salah satu penderita gagal ginjal kronis yang menjalani terapi di ruang hemodialisa dari paparan diatas penelitian ini diusulkan menggunakan aplikasi berbasis android yang memudahkan pasien untuk mengakses informasi mengenai gagal ginjal kronis selain sistem informasi aplikasi ini memiliki beberapa fitur seperti perhitungan intake output cairan reminder harian grafik untuk menggambarkan data perkembangan dan perbandingan informasi secara jelas dengan aplikasi android ini diharapkan dapat meningkatkan manejemen diri pada pasien gagal ginjal kronis dalam melakukan pembatasan asupan cairan sehingga dapat memudahkan pasien dalam pengontrolan cairan</t>
+        </is>
+      </c>
+      <c r="R49" t="n">
+        <v>0.49</v>
+      </c>
+      <c r="S49" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T49" t="inlineStr">
+        <is>
+          <t>rancang bangun alat sensor pendeteksi kekeruhan air pada bak mandi santri nurul jadid berbasis arduino uno alat ini dibuat berdasarkan latar belakang permasalahan yang ada pada lingkungan sekitar pondok pesantren nurul jadid salah satunya ialah kurangnya perawatan air sehingga air tercemar limbah berbau berwarna beracun 3b pada bak mandi yang mengakibatkan timbulnya penyakit kulit dan menjadi sarang nyamuk yang dapat menimbulkan berbagai penyakit maka dengan adanya alat yang kami rancang ini dapat membantu dalam masalah perawatan air 3b</t>
+        </is>
+      </c>
+      <c r="U49" t="n">
+        <v>0.48</v>
+      </c>
+      <c r="V49" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="W49" t="inlineStr">
+        <is>
+          <t>rancang bangun pemantau berkurangnya cairan infus berbasis arduino dan iot klinik azzaniyah nurul jadid</t>
+        </is>
+      </c>
+      <c r="X49" t="inlineStr">
+        <is>
+          <t>alat ini berguna untuk memantau cairan infus yang ada di klinik azzaniyah nurul jadid seningga memudahkan suster atau dokter memantau cairan infus agar tidak sampai bener benar habis seningga menghambat proses penyembuhan</t>
+        </is>
+      </c>
+      <c r="Y49" t="inlineStr">
+        <is>
+          <t>monitoring infus dan pulse heart rate berbasis iot</t>
+        </is>
+      </c>
+      <c r="Z49" t="inlineStr">
+        <is>
+          <t>dengan menggunakan konsep jaringan internet of things kita dapat membuat sebuah sistem yang bisa memantau infus pada pasien sensor yang di gunakan adalah sensor load cell untuk mendeteksi volume infus pada botol serta menggunakan led super bright dan photodiode yang di pasang pada drip chamber sebagai indikator yang akan mendeteksi infus menetes ketika cairan akan habis maka sensor akan memberikan pesan telegram yang masuk pada smart phone android perawat yang bertugas serta menggunakan sensor warna tcs 34725 rgb sensor untuk mendeteksi darah yang naik pada alliran selang infus yang dapat membekukan aliran infus pada selang</t>
+        </is>
+      </c>
+      <c r="AA49" t="inlineStr">
+        <is>
+          <t>aplikasi sensor tekanan pada tabung oksigen berbasis iot di rumah sakit waluyo jati menggunakan hp android</t>
+        </is>
+      </c>
+      <c r="AB49" t="inlineStr">
+        <is>
+          <t>aplikasi menggunakan sensor tekanan pada tabung oksigen berbasis iot ini memudahkan dokter dan perawat di rsud waluyo jati mempercepat pekerjaan karena data mengenai berkurangnya isi pada tabung oksigen ini langsung secara otomatis mengirimkan notifikasi ke hp android karena sampai saat ini masih menggunakan pressure indicator air</t>
+        </is>
+      </c>
+      <c r="AC49" t="inlineStr">
+        <is>
+          <t>rancang bangun sistem pengendalian persediaan air pada tandon berbasis internet of things iot untuk paseban sena hotel</t>
+        </is>
+      </c>
+      <c r="AD49" t="inlineStr">
+        <is>
+          <t>rancang bangun monitoring system otomasi water level tank dan water pump untuk gedung paseban sena hotel adalah peralatan yang menggunakan system internet of think sebagai landasan untuk mempermudah perawatan jika terjadi trobleshoting pada system manual ataupun otomatis level air tendon pompa air listrik</t>
+        </is>
+      </c>
+      <c r="AE49" t="inlineStr">
+        <is>
+          <t>rekam data self manajemen cairan pada pasien gagal ginjal kronis yang menjalani terapi hemodialisa di rsud abdoer rahem berbasis android</t>
+        </is>
+      </c>
+      <c r="AF49" t="inlineStr">
+        <is>
+          <t>penelitan ini dilakukan berlandaskan dari penelitian sebelumnya yang menjelaskan bahwa untuk meningkatkan self manajemen dalam melakukan pembatasan asupan cairan pada pasien gagal ginjal kronis salah satunya dengan cara menggunakan alat pengontrol asupan cairan menggunakan aplikasi android hal ini sesuai dengan hasil wawancara yang dilakukan dengan perawat kepala ruang hemodialisa bahwasannya terdapat permasalahan di ruang terapi hemodialisa yaitu sering didapatkan kelebihan cairan pada saat di lakukan tindakan hemodialisa pada pasien gagal ginjal kronis hal ini dikarenakan belum adanya metode yang dapat meningkatkan manajemen diri dalam melakukan pembatasan asupan cairan pada pasien gagal ginjal kronis sulit untuk mengetahui apakah asupan cairan yang di konsumsi telah mencapai batas asupan cairan yang telah ditentukan oleh dokter atau tidak selain itu pasien juga sering lupa terhadap jumlah asupan cairan yang sudah di konsumsi salah satu penderita gagal ginjal kronis yang menjalani terapi di ruang hemodialisa dari paparan diatas penelitian ini diusulkan menggunakan aplikasi berbasis android yang memudahkan pasien untuk mengakses informasi mengenai gagal ginjal kronis selain sistem informasi aplikasi ini memiliki beberapa fitur seperti perhitungan intake output cairan reminder harian grafik untuk menggambarkan data perkembangan dan perbandingan informasi secara jelas dengan aplikasi android ini diharapkan dapat meningkatkan manejemen diri pada pasien gagal ginjal kronis dalam melakukan pembatasan asupan cairan sehingga dapat memudahkan pasien dalam pengontrolan cairan</t>
+        </is>
+      </c>
+      <c r="AG49" t="inlineStr">
+        <is>
+          <t>rancang bangun alat sensor pendeteksi kekeruhan air pada bak mandi santri nurul jadid berbasis arduino uno</t>
+        </is>
+      </c>
+      <c r="AH49" t="inlineStr">
+        <is>
+          <t>alat ini dibuat berdasarkan latar belakang permasalahan yang ada pada lingkungan sekitar pondok pesantren nurul jadid salah satunya ialah kurangnya perawatan air sehingga air tercemar limbah berbau berwarna beracun 3b pada bak mandi yang mengakibatkan timbulnya penyakit kulit dan menjadi sarang nyamuk yang dapat menimbulkan berbagai penyakit maka dengan adanya alat yang kami rancang ini dapat membantu dalam masalah perawatan air 3b</t>
+        </is>
+      </c>
+    </row>
+    <row r="50">
+      <c r="A50" t="n">
+        <v>49</v>
+      </c>
+      <c r="B50" s="3" t="n">
+        <v>46202.60390353009</v>
+      </c>
+      <c r="C50" t="inlineStr">
+        <is>
+          <t>kombinasi</t>
+        </is>
+      </c>
+      <c r="D50" t="inlineStr">
+        <is>
+          <t>tes tes1111</t>
+        </is>
+      </c>
+      <c r="E50" t="inlineStr">
+        <is>
+          <t>tes tes1111</t>
+        </is>
+      </c>
+      <c r="F50" t="n">
+        <v>1</v>
+      </c>
+      <c r="G50" t="inlineStr">
+        <is>
+          <t>Sangat Unik</t>
+        </is>
+      </c>
+      <c r="H50" t="inlineStr">
+        <is>
+          <t>aplikasi perhitungan distractor analysis pada soal multiple choice berbasis java salah satu bentuk evaluasi pendidikan terutama bagi seorang guru sangatlah menjadi tuntutan dimana seorang guru harus mengetahui hasil belajar siswanya dengan serangkaian tes berupa soal-soal pada tes objektif berbentuk multiple choice setiap butir itemnya dilengkapi dengan beberapa kemungkinan jawaban option atau alternatif yang jumlahnya berkisar antara tiga sampai lima buah salah satu dari option atau alternatif tersebut merupakan jawaban yang benar dan sisanya jawaban yang salah jawaban salah inilah yang disebut dengan distractor atau pengecoh tujuan dari penelitian ini membangun sebuah sistem perangkat lunak analisis butir soal tes pilihan ganda yang layak digunakan berdasarkan akurasi perhitungan terhadap pengecoh jawaban yang benar dengan bahasa pemrograman java</t>
+        </is>
+      </c>
+      <c r="I50" t="n">
+        <v>0.47</v>
+      </c>
+      <c r="J50" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="K50" t="inlineStr">
+        <is>
+          <t>aplikasi reliabilitas soal tes pada soal tes obyektif berbasis website sebuah sistem untuk menghitung reliabilitas hasil tes obyektif sehingga dapat dijadikan keandalan atau konsistensi hasil tes apabila dilakukan secara berulang untuk melakukan pengukuran nilai tes secara obyektif dibutuhkan peserta sample size penghitungan rata-rata mean score dan standard deviasi variance kasus saat ini guru masih menghitung secara manual yang dianggap kurang efektif dan efisien sedangkan aplikasi ini bermaksud untuk memudahkan pihak guru dalam menentukan rangking dan nilai penghitungan reliabilitas hasil tes dalam satu kali input angka reliabilitas ini berkisar sebesar 0 6-0 8 jika kurang dari 0 6 dan lebih dari 0 8 maka nilai tersebut tidak reliabilitas nilai rata-rata juga dapat dilihat dengan grafik apabila standard deviasi dan rata-rata sudah diketahui juga menjadikan sekolah lebih maju dalam pembelajarannya karena disinilah tolak ukur siswa dapat diketahui oleh karena itu dirancanglah sebuah sistem aplikasi perhitungan reliabilitas soal tes berbasis website yang lebih konsisten efektif dan efisien fasilitas pada aplikasi ini adalah a login pengguna b input nilai kebenaran soal c nilai individu dan rangking d hitung rata-rata dan standard deviasi e hasil reliabilitas</t>
+        </is>
+      </c>
+      <c r="L50" t="n">
+        <v>0.46</v>
+      </c>
+      <c r="M50" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N50" t="inlineStr">
+        <is>
+          <t>sistem informasi placement test pemetaan kelas furudhul ainiyah santri baru berbasis website penelitian ini bertempat di pondok pesantren nurul jadid paiton probolinggo sistem informasi yang dibuat adalah platform placement test berbasis website website ini menggunakan framework laravel vuejs dan quasar sistem ini menggunakan user management dan microservices api dengan frontend dan backend</t>
+        </is>
+      </c>
+      <c r="O50" t="n">
+        <v>0.42</v>
+      </c>
+      <c r="P50" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q50" t="inlineStr">
+        <is>
+          <t>aplikasi perhitungan reliabilitas soal tes berbasis java sebuah sistem untuk memudahkan pihak guru dalam melakukan pengukuran nilai rata-rata mean score standart deviasi varience dan perhitungan nilai reliabilitas siswa-siswi dalam sebuah soal tes obyektif reliabilitas yang dimaksud adalah konsistensi apabila pengukuran dilakukan secara berulang perhitungan reliabilitas ini membutuhkan perhitungan rata-rata standart deviasi dan varience angka reliabilitas ini berkisar sebesar 0 6-0 8 jika melebihi angka tersebut berarti nilai tersebut tidak reliabilitas nilai rata-rata mean score juga dapat dilihat dengan grafik apabila standart deviasi dan rata-rata sudah diketahui kasus saat ini guru masih menghitung secara manual yang begitu menyita waktu akan tetapi dengan sistem aplikasi ini guru dengan mudah menentukan hasil dari reliabilitas dengan satu kali enter dan hanya satu kali inputan nilai biner saja juga menjadikan sekolah lebih maju dalam pembelajarannya karna disinilah tolak ukur siswa dapat diketahui oleh karena itu dirancanglah sebuah sistem aplikasi perhitungan reliabilitas soal tes berbasis java yang lebih konsisten efektif dan waktu yang sangat efisien fasilitas pada aplikasi ini adalah a login pengguna b input nilai kebenaran soal c nilai individu dan rangking d hitung rata-rata dan standart devisiasi e hasil reliabilitas</t>
+        </is>
+      </c>
+      <c r="R50" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="S50" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T50" t="inlineStr">
+        <is>
+          <t>metode clustering pada tes masuk peserta didik menggunakan django membuat sistem menggunakan framework django yang berbasis python sehingga proses clustering dikelola dan dianalisa berdasarkan variabel-variabel yang telah ditentukan</t>
+        </is>
+      </c>
+      <c r="U50" t="n">
+        <v>0.39</v>
+      </c>
+      <c r="V50" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="W50" t="inlineStr">
+        <is>
+          <t>tes</t>
+        </is>
+      </c>
+      <c r="X50" t="inlineStr">
+        <is>
+          <t>tes1111</t>
+        </is>
+      </c>
+      <c r="Y50" t="inlineStr">
+        <is>
+          <t>aplikasi perhitungan distractor analysis pada soal multiple choice berbasis java</t>
+        </is>
+      </c>
+      <c r="Z50" t="inlineStr">
+        <is>
+          <t>salah satu bentuk evaluasi pendidikan terutama bagi seorang guru sangatlah menjadi tuntutan dimana seorang guru harus mengetahui hasil belajar siswanya dengan serangkaian tes berupa soal-soal pada tes objektif berbentuk multiple choice setiap butir itemnya dilengkapi dengan beberapa kemungkinan jawaban option atau alternatif yang jumlahnya berkisar antara tiga sampai lima buah salah satu dari option atau alternatif tersebut merupakan jawaban yang benar dan sisanya jawaban yang salah jawaban salah inilah yang disebut dengan distractor atau pengecoh tujuan dari penelitian ini membangun sebuah sistem perangkat lunak analisis butir soal tes pilihan ganda yang layak digunakan berdasarkan akurasi perhitungan terhadap pengecoh jawaban yang benar dengan bahasa pemrograman java</t>
+        </is>
+      </c>
+      <c r="AA50" t="inlineStr">
+        <is>
+          <t>aplikasi reliabilitas soal tes pada soal tes obyektif berbasis website</t>
+        </is>
+      </c>
+      <c r="AB50" t="inlineStr">
+        <is>
+          <t>sebuah sistem untuk menghitung reliabilitas hasil tes obyektif sehingga dapat dijadikan keandalan atau konsistensi hasil tes apabila dilakukan secara berulang untuk melakukan pengukuran nilai tes secara obyektif dibutuhkan peserta sample size penghitungan rata-rata mean score dan standard deviasi variance kasus saat ini guru masih menghitung secara manual yang dianggap kurang efektif dan efisien sedangkan aplikasi ini bermaksud untuk memudahkan pihak guru dalam menentukan rangking dan nilai penghitungan reliabilitas hasil tes dalam satu kali input angka reliabilitas ini berkisar sebesar 0 6-0 8 jika kurang dari 0 6 dan lebih dari 0 8 maka nilai tersebut tidak reliabilitas nilai rata-rata juga dapat dilihat dengan grafik apabila standard deviasi dan rata-rata sudah diketahui juga menjadikan sekolah lebih maju dalam pembelajarannya karena disinilah tolak ukur siswa dapat diketahui oleh karena itu dirancanglah sebuah sistem aplikasi perhitungan reliabilitas soal tes berbasis website yang lebih konsisten efektif dan efisien fasilitas pada aplikasi ini adalah a login pengguna b input nilai kebenaran soal c nilai individu dan rangking d hitung rata-rata dan standard deviasi e hasil reliabilitas</t>
+        </is>
+      </c>
+      <c r="AC50" t="inlineStr">
+        <is>
+          <t>sistem informasi placement test pemetaan kelas furudhul ainiyah santri baru berbasis website</t>
+        </is>
+      </c>
+      <c r="AD50" t="inlineStr">
+        <is>
+          <t>penelitian ini bertempat di pondok pesantren nurul jadid paiton probolinggo sistem informasi yang dibuat adalah platform placement test berbasis website website ini menggunakan framework laravel vuejs dan quasar sistem ini menggunakan user management dan microservices api dengan frontend dan backend</t>
+        </is>
+      </c>
+      <c r="AE50" t="inlineStr">
+        <is>
+          <t>aplikasi perhitungan reliabilitas soal tes berbasis java</t>
+        </is>
+      </c>
+      <c r="AF50" t="inlineStr">
+        <is>
+          <t>sebuah sistem untuk memudahkan pihak guru dalam melakukan pengukuran nilai rata-rata mean score standart deviasi varience dan perhitungan nilai reliabilitas siswa-siswi dalam sebuah soal tes obyektif reliabilitas yang dimaksud adalah konsistensi apabila pengukuran dilakukan secara berulang perhitungan reliabilitas ini membutuhkan perhitungan rata-rata standart deviasi dan varience angka reliabilitas ini berkisar sebesar 0 6-0 8 jika melebihi angka tersebut berarti nilai tersebut tidak reliabilitas nilai rata-rata mean score juga dapat dilihat dengan grafik apabila standart deviasi dan rata-rata sudah diketahui kasus saat ini guru masih menghitung secara manual yang begitu menyita waktu akan tetapi dengan sistem aplikasi ini guru dengan mudah menentukan hasil dari reliabilitas dengan satu kali enter dan hanya satu kali inputan nilai biner saja juga menjadikan sekolah lebih maju dalam pembelajarannya karna disinilah tolak ukur siswa dapat diketahui oleh karena itu dirancanglah sebuah sistem aplikasi perhitungan reliabilitas soal tes berbasis java yang lebih konsisten efektif dan waktu yang sangat efisien fasilitas pada aplikasi ini adalah a login pengguna b input nilai kebenaran soal c nilai individu dan rangking d hitung rata-rata dan standart devisiasi e hasil reliabilitas</t>
+        </is>
+      </c>
+      <c r="AG50" t="inlineStr">
+        <is>
+          <t>metode clustering pada tes masuk peserta didik menggunakan django</t>
+        </is>
+      </c>
+      <c r="AH50" t="inlineStr">
+        <is>
+          <t>membuat sistem menggunakan framework django yang berbasis python sehingga proses clustering dikelola dan dianalisa berdasarkan variabel-variabel yang telah ditentukan</t>
+        </is>
+      </c>
+    </row>
+    <row r="51">
+      <c r="A51" t="n">
+        <v>50</v>
+      </c>
+      <c r="B51" s="3" t="n">
+        <v>46202.68180752823</v>
+      </c>
+      <c r="C51" t="inlineStr">
+        <is>
+          <t>judul</t>
+        </is>
+      </c>
+      <c r="D51" t="inlineStr">
+        <is>
+          <t>Sistem Penilaian Judul Tugas Akhir Berbasis Indobert</t>
+        </is>
+      </c>
+      <c r="E51" t="inlineStr">
+        <is>
+          <t>sistem penilaian judul tugas akhir berbasis indobert</t>
+        </is>
+      </c>
+      <c r="F51" t="n">
+        <v>0.73</v>
+      </c>
+      <c r="G51" t="inlineStr">
+        <is>
+          <t>Cukup Unik</t>
+        </is>
+      </c>
+      <c r="H51" t="inlineStr">
+        <is>
+          <t>klasifikasi judul tugas akhir menggunakan bidirectional long short term memory bilstm pada fakultas teknik universitas nurul jadid</t>
+        </is>
+      </c>
+      <c r="I51" t="n">
+        <v>0.71</v>
+      </c>
+      <c r="J51" t="inlineStr">
+        <is>
+          <t>Mirip</t>
+        </is>
+      </c>
+      <c r="K51" t="inlineStr">
+        <is>
+          <t>sistem informasi pencarian judul skripsi berbasis informasi retrival di universitas nurul jadid paiton probolinggo</t>
+        </is>
+      </c>
+      <c r="L51" t="n">
+        <v>0.57</v>
+      </c>
+      <c r="M51" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="N51" t="inlineStr">
+        <is>
+          <t>pengembangan aplikasi pengajuan judul skripsi di universitas nurul jadid paiton probolinggo berbasis web menggunakan laravel 5 4</t>
+        </is>
+      </c>
+      <c r="O51" t="n">
+        <v>0.54</v>
+      </c>
+      <c r="P51" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="Q51" t="inlineStr">
+        <is>
+          <t>sistem rekomendasi mata kuliah pilihan menggunakan metode item-based collaborative filtering</t>
+        </is>
+      </c>
+      <c r="R51" t="n">
+        <v>0.51</v>
+      </c>
+      <c r="S51" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="T51" t="inlineStr">
+        <is>
+          <t>pengembangan aplikasi karya tulis non-ilmiah mahasiswa universitas nurul jadid berbasis web</t>
+        </is>
+      </c>
+      <c r="U51" t="n">
+        <v>0.5</v>
+      </c>
+      <c r="V51" t="inlineStr">
+        <is>
+          <t>Tidak Mirip</t>
+        </is>
+      </c>
+      <c r="W51" t="inlineStr"/>
+      <c r="X51" t="inlineStr"/>
+      <c r="Y51" t="inlineStr"/>
+      <c r="Z51" t="inlineStr"/>
+      <c r="AA51" t="inlineStr"/>
+      <c r="AB51" t="inlineStr"/>
+      <c r="AC51" t="inlineStr"/>
+      <c r="AD51" t="inlineStr"/>
+      <c r="AE51" t="inlineStr"/>
+      <c r="AF51" t="inlineStr"/>
+      <c r="AG51" t="inlineStr"/>
+      <c r="AH51" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
